--- a/config/auto_configs/2024_Hyundai_Genesis_GV60 EV(JW1 EV)_160kW+160kW.xlsx
+++ b/config/auto_configs/2024_Hyundai_Genesis_GV60 EV(JW1 EV)_160kW+160kW.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NWS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NWS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,7 +547,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GMA_10001</t>
+          <t>GMA_10005</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GMA_10005</t>
+          <t>GMA_10001</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -578,6 +578,1260 @@
         </is>
       </c>
       <c r="D4" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>IBU-TPMS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GMA_USA_00813</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A/C</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GMA_USA_00814</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ADAS_D</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GMA_USA_00216</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ADAS_P</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GMA_USA_00837</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AFCU</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GMA_10014</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AMP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GMA_10007</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>APSS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GMA_USA_00847</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>APSU</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GMA_USA_00843</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BMS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GMA_10006</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CCIC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GMA_10023</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CCU_CCNF</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GMA_10019</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CCU_CGW</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GMA_10020</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GMA_10013</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GMA_USA_00842</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DAU</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>GMA_10012</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DCU</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>GMA_10021</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DLBCU</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>GMA_USA_00844</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DPSS</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>GMA_USA_00848</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DSM-L</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>GMA_10015</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DSM-R</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>GMA_10016</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DVRS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>GMA_USA_00839</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ECS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GMA_USA_00817</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ELSD</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>GMA_USA_00835</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>GMA_USA_00815</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>E-Shifter</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>GMA_USA_00831</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>FPM</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>GMA_10022</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>GMA_USA_00840</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>FRU</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>GMA_10024</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FVC</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>GMA_USA_00833</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>IAU</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>GMA_USA_00838</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>IBU-BCM</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>GMA_USA_00829</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>IBU-SKU</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>GMA_USA_00832</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ICCU</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>GMA_USA_00215</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ICU</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>GMA_USA_00834</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ILCU-LH</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>GMA_USA_00849</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ILCU-RH</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>GMA_USA_00850</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MCU-F</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>GMA_10002</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MCU-R</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>GMA_10003</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MFS</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>GMA_USA_00822</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MLM</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>GMA_USA_00836</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>OCS</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>GMA_USA_00827</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>OMS</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>GMA_10018</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PCM</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>GMA_USA_00217</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PSB</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>GMA_USA_00818</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PSM</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>GMA_USA_00821</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PTG</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>GMA_USA_00816</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ROA</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>GMA_10017</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SCM</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>GMA_USA_00823</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SCU</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>GMA_10009</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SHVU-F</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>GMA_10010</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SHVU-R</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>GMA_10011</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SWRC</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>GMA_USA_00824</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>VCMS</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>GMA_USA_00213</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>VCU</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>GMA_USA_00218</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>VESS</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>GMA_10008</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>WCCU</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>GMA_10025</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>WPC</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>GMA_USA_00830</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>00</t>
         </is>
